--- a/products-storage/08-pto-bez-zamechaniy/07-grafik-ustraneniya.xlsx
+++ b/products-storage/08-pto-bez-zamechaniy/07-grafik-ustraneniya.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2">
-        <f>СРЗНАЧ(G2:G20)</f>
+        <f>AVERAGE(G2:G3)</f>
         <v/>
       </c>
       <c r="H4" s="2" t="inlineStr"/>

--- a/products-storage/08-pto-bez-zamechaniy/07-grafik-ustraneniya.xlsx
+++ b/products-storage/08-pto-bez-zamechaniy/07-grafik-ustraneniya.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График устранения замечаний" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'График устранения замечаний'!$A$1:$H$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -434,7 +436,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -546,5 +548,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>